--- a/output/pdf_financials_xlsx/BTU.xlsx
+++ b/output/pdf_financials_xlsx/BTU.xlsx
@@ -1140,7 +1140,7 @@
         <v>-0.681122</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.710476</v>
+        <v>-0.710476</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-0.550905</v>
@@ -1380,7 +1380,7 @@
         <v>-0.681122</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.710476</v>
+        <v>-0.710476</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-0.550905</v>
@@ -1522,7 +1522,7 @@
         <v>-0.681122</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.710476</v>
+        <v>-0.710476</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-0.550905</v>
@@ -1668,7 +1668,7 @@
         <v>17.02805</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>35.5238</v>
+        <v>-35.5238</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>-0.681122</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.710476</v>
+        <v>-0.710476</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.550905</v>
@@ -1816,7 +1816,7 @@
         <v>-0.681122</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.710476</v>
+        <v>-0.710476</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.550905</v>
@@ -1936,7 +1936,7 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.173291</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.173291</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
@@ -4900,19 +4900,19 @@
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.971289</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.993269</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.709714</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.709714</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.709714</v>
       </c>
     </row>
     <row r="93">
@@ -6078,10 +6078,10 @@
         <v>0</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>2.128083</v>
+        <v>1.715914</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.323265</v>
       </c>
     </row>
     <row r="119">
@@ -7801,7 +7801,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -18287,7 +18291,11 @@
           <t>Share-Based Payment Reserve</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -20130,7 +20138,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -35102,10 +35114,10 @@
         <v>-0.681122</v>
       </c>
       <c r="L350" s="5" t="n">
-        <v>0.710476</v>
+        <v>-0.710476</v>
       </c>
       <c r="M350" s="5" t="n">
-        <v>0.550905</v>
+        <v>-0.550905</v>
       </c>
       <c r="N350" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BTU.xlsx
+++ b/output/pdf_financials_xlsx/BTU.xlsx
@@ -951,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00885</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002986</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.061653</v>
       </c>
     </row>
     <row r="13">
@@ -1723,10 +1723,10 @@
         <v>-0.710476</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.550905</v>
+        <v>-0.542055</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.520737</v>
+        <v>-1.517751</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.697611</v>
@@ -1735,7 +1735,7 @@
         <v>-3.666626</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.148108</v>
+        <v>-0.209761</v>
       </c>
     </row>
     <row r="28">
@@ -1819,10 +1819,10 @@
         <v>-0.710476</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.550905</v>
+        <v>-0.542055</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.520737</v>
+        <v>-1.517751</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.697611</v>
@@ -1831,7 +1831,7 @@
         <v>-3.666626</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.148108</v>
+        <v>-0.209761</v>
       </c>
     </row>
     <row r="30">
@@ -2057,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.01793</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.224972</v>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.01793</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.224972</v>
@@ -2729,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.01793</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.405391</v>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -32517,7 +32517,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -38511,7 +38511,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
